--- a/artfynd/A 55622-2024 artfynd.xlsx
+++ b/artfynd/A 55622-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128657803</v>
       </c>
       <c r="B2" t="n">
-        <v>98496</v>
+        <v>98502</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55622-2024 artfynd.xlsx
+++ b/artfynd/A 55622-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128657803</v>
       </c>
       <c r="B2" t="n">
-        <v>98502</v>
+        <v>98505</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55622-2024 artfynd.xlsx
+++ b/artfynd/A 55622-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128657803</v>
       </c>
       <c r="B2" t="n">
-        <v>98505</v>
+        <v>98508</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55622-2024 artfynd.xlsx
+++ b/artfynd/A 55622-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128657803</v>
       </c>
       <c r="B2" t="n">
-        <v>98508</v>
+        <v>98509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55622-2024 artfynd.xlsx
+++ b/artfynd/A 55622-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128657803</v>
       </c>
       <c r="B2" t="n">
-        <v>98509</v>
+        <v>98536</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55622-2024 artfynd.xlsx
+++ b/artfynd/A 55622-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128657803</v>
       </c>
       <c r="B2" t="n">
-        <v>98536</v>
+        <v>98542</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55622-2024 artfynd.xlsx
+++ b/artfynd/A 55622-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128657803</v>
       </c>
       <c r="B2" t="n">
-        <v>98542</v>
+        <v>98549</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55622-2024 artfynd.xlsx
+++ b/artfynd/A 55622-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128657803</v>
       </c>
       <c r="B2" t="n">
-        <v>98549</v>
+        <v>98553</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55622-2024 artfynd.xlsx
+++ b/artfynd/A 55622-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128657803</v>
       </c>
       <c r="B2" t="n">
-        <v>98553</v>
+        <v>98560</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55622-2024 artfynd.xlsx
+++ b/artfynd/A 55622-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128657803</v>
       </c>
       <c r="B2" t="n">
-        <v>98563</v>
+        <v>98568</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55622-2024 artfynd.xlsx
+++ b/artfynd/A 55622-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128657803</v>
       </c>
       <c r="B2" t="n">
-        <v>98568</v>
+        <v>98576</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55622-2024 artfynd.xlsx
+++ b/artfynd/A 55622-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128657803</v>
       </c>
       <c r="B2" t="n">
-        <v>98576</v>
+        <v>98586</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55622-2024 artfynd.xlsx
+++ b/artfynd/A 55622-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128657803</v>
       </c>
       <c r="B2" t="n">
-        <v>98586</v>
+        <v>99035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
